--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -53,269 +53,1289 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.453125" customWidth="true"/>
     <col min="2" max="2" width="13.453125" customWidth="true"/>
     <col min="3" max="3" width="11.453125" customWidth="true"/>
-    <col min="4" max="4" width="12.453125" customWidth="true"/>
+    <col min="4" max="4" width="13.453125" customWidth="true"/>
     <col min="5" max="5" width="15.453125" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0">
-        <v>0.22176367606154754</v>
+        <v>0.43006027248385487</v>
       </c>
       <c r="B1" s="0">
-        <v>0.059342310880851477</v>
+        <v>0.13453488149209417</v>
       </c>
       <c r="C1" s="0">
-        <v>1.513808342273647</v>
+        <v>1.432233268043384</v>
       </c>
       <c r="D1" s="0">
-        <v>1.2309282130873864</v>
+        <v>2.5330713206692268</v>
       </c>
       <c r="E1" s="0">
-        <v>0.00050828320559270182</v>
+        <v>9.6484531346397389e-05</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>0.32473144116695835</v>
+        <v>0.58769676246723046</v>
       </c>
       <c r="B2" s="0">
-        <v>0.11909644178987432</v>
+        <v>0.13021975339121736</v>
       </c>
       <c r="C2" s="0">
-        <v>1.4964085929957633</v>
+        <v>1.5359584708558867</v>
       </c>
       <c r="D2" s="0">
-        <v>1.0529363037610366</v>
+        <v>0.39940477735905561</v>
       </c>
       <c r="E2" s="0">
-        <v>0.00055022249700236207</v>
+        <v>2.9243222551417485e-05</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.56432391300692308</v>
+        <v>0.9999999830159737</v>
       </c>
       <c r="B3" s="0">
-        <v>0.14565947353953146</v>
+        <v>0.17661632942246586</v>
       </c>
       <c r="C3" s="0">
-        <v>1.640723280152844</v>
+        <v>2.0764418952222758</v>
       </c>
       <c r="D3" s="0">
-        <v>1.0056209109917909</v>
+        <v>0.19795165707250453</v>
       </c>
       <c r="E3" s="0">
-        <v>0.00061233044375456718</v>
+        <v>0.054588803615128682</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.46913480662901258</v>
+        <v>0.45287088618585314</v>
       </c>
       <c r="B4" s="0">
-        <v>0.057488786909511924</v>
+        <v>0.07252944687279568</v>
       </c>
       <c r="C4" s="0">
-        <v>1.5189214557901527</v>
+        <v>1.5505765781898662</v>
       </c>
       <c r="D4" s="0">
-        <v>1.8734235241211525</v>
+        <v>1.8713857301755468</v>
       </c>
       <c r="E4" s="0">
-        <v>0.00050230758024864645</v>
+        <v>0.00032507078991244557</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.89244981573469562</v>
+        <v>0.89471279275846016</v>
       </c>
       <c r="B5" s="0">
-        <v>0.081642191216504886</v>
+        <v>0.089647374555226894</v>
       </c>
       <c r="C5" s="0">
-        <v>1.5329171355725022</v>
+        <v>1.5486300366703338</v>
       </c>
       <c r="D5" s="0">
-        <v>1.7778875069926667</v>
+        <v>1.0614159133655754</v>
       </c>
       <c r="E5" s="0">
-        <v>0.00052889552060216667</v>
+        <v>0.00011644379226782769</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.75780333298527358</v>
+        <v>0.90986627095651584</v>
       </c>
       <c r="B6" s="0">
-        <v>0.15872145562222162</v>
+        <v>0.17400293208743123</v>
       </c>
       <c r="C6" s="0">
-        <v>1.5293918377324254</v>
+        <v>1.5187028995894041</v>
       </c>
       <c r="D6" s="0">
-        <v>1.9203804414133436</v>
+        <v>1.839716949978615</v>
       </c>
       <c r="E6" s="0">
-        <v>0.00051832878781188948</v>
+        <v>9.5658695074287594e-06</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>0.81335304547649512</v>
+        <v>0.99999999889447699</v>
       </c>
       <c r="B7" s="0">
-        <v>0.19568796412024611</v>
+        <v>0.19997142479636143</v>
       </c>
       <c r="C7" s="0">
-        <v>1.5342054081329517</v>
+        <v>1.5526294444580688</v>
       </c>
       <c r="D7" s="0">
-        <v>1.7973528864566075</v>
+        <v>1.9919363825158358</v>
       </c>
       <c r="E7" s="0">
-        <v>0.00058710004116084829</v>
+        <v>0.41691368240819315</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>0.77039181014948266</v>
+        <v>0.9161894193284702</v>
       </c>
       <c r="B8" s="0">
-        <v>0.098122259243736243</v>
+        <v>0.038429388852132346</v>
       </c>
       <c r="C8" s="0">
-        <v>3.6156391693223391</v>
+        <v>3.6353361049360986</v>
       </c>
       <c r="D8" s="0">
-        <v>0.7662535604327283</v>
+        <v>0.7168416486946444</v>
       </c>
       <c r="E8" s="0">
-        <v>0.00016319384535927404</v>
+        <v>0.00032549854036428947</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>0.56456072719100803</v>
+        <v>0.48738250672896449</v>
       </c>
       <c r="B9" s="0">
-        <v>0.16319523731678751</v>
+        <v>0.13677105473850162</v>
       </c>
       <c r="C9" s="0">
-        <v>3.6059563354533699</v>
+        <v>3.6202139632669117</v>
       </c>
       <c r="D9" s="0">
-        <v>0.69432703009860464</v>
+        <v>1.2346823120519392</v>
       </c>
       <c r="E9" s="0">
-        <v>0.00015151190184287691</v>
+        <v>0.00022395489190543726</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>0.68268348855866978</v>
+        <v>0.99999994202455189</v>
       </c>
       <c r="B10" s="0">
-        <v>0.20000000000000001</v>
+        <v>0.1919586794279492</v>
       </c>
       <c r="C10" s="0">
-        <v>3.6387187645288681</v>
+        <v>3.6563015717385894</v>
       </c>
       <c r="D10" s="0">
-        <v>0.75055341535926012</v>
+        <v>0.39632789308947769</v>
       </c>
       <c r="E10" s="0">
-        <v>0.00043757107107793996</v>
+        <v>0.0042744076442370327</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>0.27251414345506614</v>
+        <v>0.37971736574572823</v>
       </c>
       <c r="B11" s="0">
-        <v>0.20000000000000001</v>
+        <v>0.1999893031208137</v>
       </c>
       <c r="C11" s="0">
-        <v>3.6022784614867636</v>
+        <v>3.6403668098117561</v>
       </c>
       <c r="D11" s="0">
-        <v>0.931534869561914</v>
+        <v>0.64078702360810769</v>
       </c>
       <c r="E11" s="0">
-        <v>0.0007375398737815166</v>
+        <v>0.00013697912328792204</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>0.37803624346276793</v>
+        <v>0.99999999864380396</v>
       </c>
       <c r="B12" s="0">
-        <v>0.16359079629866807</v>
+        <v>0.10967644542390596</v>
       </c>
       <c r="C12" s="0">
-        <v>3.6155154530653713</v>
+        <v>3.6285518854547618</v>
       </c>
       <c r="D12" s="0">
-        <v>1.7067986736798213</v>
+        <v>2.8329893700099178</v>
       </c>
       <c r="E12" s="0">
-        <v>0.00014150810867615636</v>
+        <v>0.12081940404271573</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>0.71745780640050827</v>
+        <v>0.74724988382408464</v>
       </c>
       <c r="B13" s="0">
-        <v>0.13770541885089554</v>
+        <v>0.10545453658921036</v>
       </c>
       <c r="C13" s="0">
-        <v>3.6275008130108692</v>
+        <v>3.6478327632180116</v>
       </c>
       <c r="D13" s="0">
-        <v>1.552743408787387</v>
+        <v>1.2151299398891509</v>
       </c>
       <c r="E13" s="0">
-        <v>0.00015097595739252295</v>
+        <v>0.00069035096940398932</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>0.3901983724056291</v>
+        <v>0.80720733107969367</v>
       </c>
       <c r="B14" s="0">
-        <v>0.20000000000000001</v>
+        <v>0.14530650550568239</v>
       </c>
       <c r="C14" s="0">
-        <v>3.6089678133182845</v>
+        <v>3.6356183438564846</v>
       </c>
       <c r="D14" s="0">
-        <v>1.6469615184258746</v>
+        <v>2.4344635122036231</v>
       </c>
       <c r="E14" s="0">
-        <v>0.00023391561709442866</v>
+        <v>3.5048514436845549e-06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>0.27706743788870136</v>
+        <v>0.32298974880165993</v>
       </c>
       <c r="B15" s="0">
-        <v>0.20000000000000001</v>
+        <v>0.15279036836360094</v>
       </c>
       <c r="C15" s="0">
-        <v>3.5977044030213592</v>
+        <v>3.6363915283198325</v>
       </c>
       <c r="D15" s="0">
-        <v>2.0078134945690356</v>
+        <v>2.2275942751106532</v>
       </c>
       <c r="E15" s="0">
-        <v>0.00050781992633800897</v>
+        <v>3.7474776519599992e-05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0">
+        <v>0.9405587483753105</v>
+      </c>
+      <c r="B16" s="0">
+        <v>0.059306798612050092</v>
+      </c>
+      <c r="C16" s="0">
+        <v>1.691501564240208</v>
+      </c>
+      <c r="D16" s="0">
+        <v>0.18361991572574529</v>
+      </c>
+      <c r="E16" s="0">
+        <v>0.00012778978791971949</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0">
+        <v>0.66223874981484776</v>
+      </c>
+      <c r="B17" s="0">
+        <v>0.11117332548937459</v>
+      </c>
+      <c r="C17" s="0">
+        <v>1.5259492118064888</v>
+      </c>
+      <c r="D17" s="0">
+        <v>2.6285808216274744</v>
+      </c>
+      <c r="E17" s="0">
+        <v>5.8972898051252724e-05</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0">
+        <v>0.65401907659250758</v>
+      </c>
+      <c r="B18" s="0">
+        <v>0.19483534828164387</v>
+      </c>
+      <c r="C18" s="0">
+        <v>1.8482982025617829</v>
+      </c>
+      <c r="D18" s="0">
+        <v>0.47592096695569946</v>
+      </c>
+      <c r="E18" s="0">
+        <v>0.00019757241216439037</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0">
+        <v>0.67563846576722231</v>
+      </c>
+      <c r="B19" s="0">
+        <v>0.07945156401384508</v>
+      </c>
+      <c r="C19" s="0">
+        <v>1.5877843651336752</v>
+      </c>
+      <c r="D19" s="0">
+        <v>0.61187032049741563</v>
+      </c>
+      <c r="E19" s="0">
+        <v>0.00063732066355295404</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0">
+        <v>0.93448720067759961</v>
+      </c>
+      <c r="B20" s="0">
+        <v>0.069014244029556748</v>
+      </c>
+      <c r="C20" s="0">
+        <v>1.5464861793569937</v>
+      </c>
+      <c r="D20" s="0">
+        <v>1.975016094327672</v>
+      </c>
+      <c r="E20" s="0">
+        <v>8.9780080853017134e-07</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0">
+        <v>0.74888879778217454</v>
+      </c>
+      <c r="B21" s="0">
+        <v>0.19999962094528317</v>
+      </c>
+      <c r="C21" s="0">
+        <v>1.951515908485985</v>
+      </c>
+      <c r="D21" s="0">
+        <v>0.33205610643415745</v>
+      </c>
+      <c r="E21" s="0">
+        <v>0.0043309510311028568</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0">
+        <v>0.76716301803104847</v>
+      </c>
+      <c r="B22" s="0">
+        <v>0.19999277077119079</v>
+      </c>
+      <c r="C22" s="0">
+        <v>1.5388129679282967</v>
+      </c>
+      <c r="D22" s="0">
+        <v>1.8163451252177127</v>
+      </c>
+      <c r="E22" s="0">
+        <v>0.00024240582478238273</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0">
+        <v>0.62249175209125196</v>
+      </c>
+      <c r="B23" s="0">
+        <v>0.089545508590291034</v>
+      </c>
+      <c r="C23" s="0">
+        <v>3.6316348750394352</v>
+      </c>
+      <c r="D23" s="0">
+        <v>1.2943998464064648</v>
+      </c>
+      <c r="E23" s="0">
+        <v>7.6499703745618858e-07</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0">
+        <v>0.90184815226925241</v>
+      </c>
+      <c r="B24" s="0">
+        <v>0.091021918116675912</v>
+      </c>
+      <c r="C24" s="0">
+        <v>3.6249990543983159</v>
+      </c>
+      <c r="D24" s="0">
+        <v>0.49297436520503291</v>
+      </c>
+      <c r="E24" s="0">
+        <v>3.0218680910829251e-05</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0">
+        <v>0.6606159255193842</v>
+      </c>
+      <c r="B25" s="0">
+        <v>0.18547248763479507</v>
+      </c>
+      <c r="C25" s="0">
+        <v>3.6515223733196902</v>
+      </c>
+      <c r="D25" s="0">
+        <v>0.91214411766397929</v>
+      </c>
+      <c r="E25" s="0">
+        <v>1.4011272641540133e-05</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0">
+        <v>0.93417233053654958</v>
+      </c>
+      <c r="B26" s="0">
+        <v>0.12033561465902946</v>
+      </c>
+      <c r="C26" s="0">
+        <v>3.638846397424818</v>
+      </c>
+      <c r="D26" s="0">
+        <v>0.26190470813452527</v>
+      </c>
+      <c r="E26" s="0">
+        <v>1.3924196075810549e-05</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0">
+        <v>0.42460617239234055</v>
+      </c>
+      <c r="B27" s="0">
+        <v>0.13855539608197937</v>
+      </c>
+      <c r="C27" s="0">
+        <v>3.6384487007227544</v>
+      </c>
+      <c r="D27" s="0">
+        <v>1.0670723099082475</v>
+      </c>
+      <c r="E27" s="0">
+        <v>7.6092978332929212e-05</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="0">
+        <v>0.99999999856386224</v>
+      </c>
+      <c r="B28" s="0">
+        <v>0.11523387157515391</v>
+      </c>
+      <c r="C28" s="0">
+        <v>3.6442451667299292</v>
+      </c>
+      <c r="D28" s="0">
+        <v>2.2398532112211207</v>
+      </c>
+      <c r="E28" s="0">
+        <v>0.004568613402173901</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="0">
+        <v>0.46337823745896534</v>
+      </c>
+      <c r="B29" s="0">
+        <v>0.14602633148466815</v>
+      </c>
+      <c r="C29" s="0">
+        <v>3.6193861346758021</v>
+      </c>
+      <c r="D29" s="0">
+        <v>0.72319951101572322</v>
+      </c>
+      <c r="E29" s="0">
+        <v>0.0008288808426985321</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="0">
+        <v>0.55500429597037904</v>
+      </c>
+      <c r="B30" s="0">
+        <v>0.1997989167289286</v>
+      </c>
+      <c r="C30" s="0">
+        <v>3.6271962619376414</v>
+      </c>
+      <c r="D30" s="0">
+        <v>2.2872074152729729</v>
+      </c>
+      <c r="E30" s="0">
+        <v>0.0001066079783719669</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="0">
+        <v>0.24790016358059389</v>
+      </c>
+      <c r="B31" s="0">
+        <v>0.037324551253691496</v>
+      </c>
+      <c r="C31" s="0">
+        <v>1.5689834115959183</v>
+      </c>
+      <c r="D31" s="0">
+        <v>0.87964503611748801</v>
+      </c>
+      <c r="E31" s="0">
+        <v>9.7915715994349313e-05</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="0">
+        <v>0.99999999932899575</v>
+      </c>
+      <c r="B32" s="0">
+        <v>0.18366559292325332</v>
+      </c>
+      <c r="C32" s="0">
+        <v>1.5372097192365997</v>
+      </c>
+      <c r="D32" s="0">
+        <v>0.088263284853650412</v>
+      </c>
+      <c r="E32" s="0">
+        <v>0.26170532851811618</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="0">
+        <v>0.92919559288533504</v>
+      </c>
+      <c r="B33" s="0">
+        <v>0.1276660367102973</v>
+      </c>
+      <c r="C33" s="0">
+        <v>1.5394478770640041</v>
+      </c>
+      <c r="D33" s="0">
+        <v>2.252464417218548</v>
+      </c>
+      <c r="E33" s="0">
+        <v>4.8896489541137608e-05</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="0">
+        <v>0.42457339818475265</v>
+      </c>
+      <c r="B34" s="0">
+        <v>0.041177948967131894</v>
+      </c>
+      <c r="C34" s="0">
+        <v>1.5558213741412616</v>
+      </c>
+      <c r="D34" s="0">
+        <v>1.4927494087853364</v>
+      </c>
+      <c r="E34" s="0">
+        <v>2.0518806755610463e-05</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="0">
+        <v>0.89204698118574532</v>
+      </c>
+      <c r="B35" s="0">
+        <v>0.088758920303831104</v>
+      </c>
+      <c r="C35" s="0">
+        <v>1.5458204963518134</v>
+      </c>
+      <c r="D35" s="0">
+        <v>1.0715329919432246</v>
+      </c>
+      <c r="E35" s="0">
+        <v>7.5440512028549732e-06</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="0">
+        <v>0.91522554515488341</v>
+      </c>
+      <c r="B36" s="0">
+        <v>0.16951944380750075</v>
+      </c>
+      <c r="C36" s="0">
+        <v>1.5300675973414193</v>
+      </c>
+      <c r="D36" s="0">
+        <v>1.9042418697374333</v>
+      </c>
+      <c r="E36" s="0">
+        <v>0.00034385744210424572</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="0">
+        <v>0.46720838642391066</v>
+      </c>
+      <c r="B37" s="0">
+        <v>0.19998024281224575</v>
+      </c>
+      <c r="C37" s="0">
+        <v>1.5561423586566936</v>
+      </c>
+      <c r="D37" s="0">
+        <v>0.66283026083477126</v>
+      </c>
+      <c r="E37" s="0">
+        <v>0.0019664443473867404</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="0">
+        <v>0.78264520846885122</v>
+      </c>
+      <c r="B38" s="0">
+        <v>0.047836013986986718</v>
+      </c>
+      <c r="C38" s="0">
+        <v>3.6319739872495695</v>
+      </c>
+      <c r="D38" s="0">
+        <v>0.87479073428939291</v>
+      </c>
+      <c r="E38" s="0">
+        <v>3.6391372387243104e-06</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="0">
+        <v>0.50149789574071613</v>
+      </c>
+      <c r="B39" s="0">
+        <v>0.088811705303834684</v>
+      </c>
+      <c r="C39" s="0">
+        <v>3.6233042390181591</v>
+      </c>
+      <c r="D39" s="0">
+        <v>1.7675274392734248</v>
+      </c>
+      <c r="E39" s="0">
+        <v>9.6524162209221667e-05</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="0">
+        <v>0.92663650026208366</v>
+      </c>
+      <c r="B40" s="0">
+        <v>0.15912819120641333</v>
+      </c>
+      <c r="C40" s="0">
+        <v>3.6561747094357862</v>
+      </c>
+      <c r="D40" s="0">
+        <v>0.54964614487262387</v>
+      </c>
+      <c r="E40" s="0">
+        <v>0.00030028967771992865</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="0">
+        <v>0.26399021173053527</v>
+      </c>
+      <c r="B41" s="0">
+        <v>0.19993997440386616</v>
+      </c>
+      <c r="C41" s="0">
+        <v>3.6185338306054935</v>
+      </c>
+      <c r="D41" s="0">
+        <v>1.1243720561038775</v>
+      </c>
+      <c r="E41" s="0">
+        <v>0.0005155147554344664</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="0">
+        <v>0.83543120891222133</v>
+      </c>
+      <c r="B42" s="0">
+        <v>0.12098226776613112</v>
+      </c>
+      <c r="C42" s="0">
+        <v>3.6476484091674268</v>
+      </c>
+      <c r="D42" s="0">
+        <v>0.43982936517672416</v>
+      </c>
+      <c r="E42" s="0">
+        <v>3.4795860631670328e-05</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="0">
+        <v>0.74594220791452459</v>
+      </c>
+      <c r="B43" s="0">
+        <v>0.13497914485046567</v>
+      </c>
+      <c r="C43" s="0">
+        <v>3.6450645300341717</v>
+      </c>
+      <c r="D43" s="0">
+        <v>1.1303423445902421</v>
+      </c>
+      <c r="E43" s="0">
+        <v>0.00016085064543484371</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="0">
+        <v>0.8155514038266517</v>
+      </c>
+      <c r="B44" s="0">
+        <v>0.12660070135077722</v>
+      </c>
+      <c r="C44" s="0">
+        <v>3.639303458167281</v>
+      </c>
+      <c r="D44" s="0">
+        <v>2.5262602124448077</v>
+      </c>
+      <c r="E44" s="0">
+        <v>1.3296216072614182e-05</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="0">
+        <v>0.22989720359626439</v>
+      </c>
+      <c r="B45" s="0">
+        <v>0.13621787013559267</v>
+      </c>
+      <c r="C45" s="0">
+        <v>3.653201493983095</v>
+      </c>
+      <c r="D45" s="0">
+        <v>1.6782783671674468</v>
+      </c>
+      <c r="E45" s="0">
+        <v>0.00010721806842283012</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="0">
+        <v>0.99999989188604377</v>
+      </c>
+      <c r="B46" s="0">
+        <v>0.14433324429146324</v>
+      </c>
+      <c r="C46" s="0">
+        <v>1.2578731034221362</v>
+      </c>
+      <c r="D46" s="0">
+        <v>2.7621188464290309</v>
+      </c>
+      <c r="E46" s="0">
+        <v>0.039813199005491455</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="0">
+        <v>0.30605118099355655</v>
+      </c>
+      <c r="B47" s="0">
+        <v>0.15536714374238006</v>
+      </c>
+      <c r="C47" s="0">
+        <v>1.5269959373433288</v>
+      </c>
+      <c r="D47" s="0">
+        <v>1.8372848177613894</v>
+      </c>
+      <c r="E47" s="0">
+        <v>3.2204976023159556e-05</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="0">
+        <v>0.87139079578312673</v>
+      </c>
+      <c r="B48" s="0">
+        <v>0.16854941747069194</v>
+      </c>
+      <c r="C48" s="0">
+        <v>1.856622182528699</v>
+      </c>
+      <c r="D48" s="0">
+        <v>0.34433796626609237</v>
+      </c>
+      <c r="E48" s="0">
+        <v>0.00014344294537111882</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="0">
+        <v>0.69228247420147349</v>
+      </c>
+      <c r="B49" s="0">
+        <v>0.038880295463741069</v>
+      </c>
+      <c r="C49" s="0">
+        <v>1.5338555520846329</v>
+      </c>
+      <c r="D49" s="0">
+        <v>2.4637471593631881</v>
+      </c>
+      <c r="E49" s="0">
+        <v>7.6646077407041834e-05</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="0">
+        <v>0.84333489670474904</v>
+      </c>
+      <c r="B50" s="0">
+        <v>0.095980655533944789</v>
+      </c>
+      <c r="C50" s="0">
+        <v>1.5482837422209448</v>
+      </c>
+      <c r="D50" s="0">
+        <v>1.2405617000130127</v>
+      </c>
+      <c r="E50" s="0">
+        <v>7.7347001315491596e-05</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="0">
+        <v>0.73181112386982272</v>
+      </c>
+      <c r="B51" s="0">
+        <v>0.1952023994727147</v>
+      </c>
+      <c r="C51" s="0">
+        <v>1.9150600437532472</v>
+      </c>
+      <c r="D51" s="0">
+        <v>0.3459323809287338</v>
+      </c>
+      <c r="E51" s="0">
+        <v>0.0040584388152241435</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="0">
+        <v>0.77082974704869711</v>
+      </c>
+      <c r="B52" s="0">
+        <v>0.19872364768564849</v>
+      </c>
+      <c r="C52" s="0">
+        <v>1.5503143275744553</v>
+      </c>
+      <c r="D52" s="0">
+        <v>1.8230851981787248</v>
+      </c>
+      <c r="E52" s="0">
+        <v>3.8423879326442343e-05</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="0">
+        <v>0.99999999971458786</v>
+      </c>
+      <c r="B53" s="0">
+        <v>0.12288709782317013</v>
+      </c>
+      <c r="C53" s="0">
+        <v>3.6302778889271092</v>
+      </c>
+      <c r="D53" s="0">
+        <v>0.35831614373988963</v>
+      </c>
+      <c r="E53" s="0">
+        <v>0.10292034726474653</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="0">
+        <v>0.51160485420621415</v>
+      </c>
+      <c r="B54" s="0">
+        <v>0.098123213686562114</v>
+      </c>
+      <c r="C54" s="0">
+        <v>3.6372195338257338</v>
+      </c>
+      <c r="D54" s="0">
+        <v>1.1422788503241521</v>
+      </c>
+      <c r="E54" s="0">
+        <v>0.00075088996588376362</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="0">
+        <v>0.77463449869656442</v>
+      </c>
+      <c r="B55" s="0">
+        <v>0.16410668403068643</v>
+      </c>
+      <c r="C55" s="0">
+        <v>3.6483158120505634</v>
+      </c>
+      <c r="D55" s="0">
+        <v>1.800552104958224</v>
+      </c>
+      <c r="E55" s="0">
+        <v>6.0759586038992233e-07</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="0">
+        <v>0.4501130637468434</v>
+      </c>
+      <c r="B56" s="0">
+        <v>0.18226922669964982</v>
+      </c>
+      <c r="C56" s="0">
+        <v>3.6373076741646924</v>
+      </c>
+      <c r="D56" s="0">
+        <v>0.52643765256866859</v>
+      </c>
+      <c r="E56" s="0">
+        <v>2.923815812260051e-05</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="0">
+        <v>0.99999971967677248</v>
+      </c>
+      <c r="B57" s="0">
+        <v>0.15511710614632992</v>
+      </c>
+      <c r="C57" s="0">
+        <v>3.6486599605200851</v>
+      </c>
+      <c r="D57" s="0">
+        <v>0.28815141288536766</v>
+      </c>
+      <c r="E57" s="0">
+        <v>0.02717699325389741</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="0">
+        <v>0.72887149549375096</v>
+      </c>
+      <c r="B58" s="0">
+        <v>0.14358483266239161</v>
+      </c>
+      <c r="C58" s="0">
+        <v>3.6433908746563848</v>
+      </c>
+      <c r="D58" s="0">
+        <v>1.4293919605957202</v>
+      </c>
+      <c r="E58" s="0">
+        <v>6.8417154214801349e-05</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="0">
+        <v>0.65560900544394851</v>
+      </c>
+      <c r="B59" s="0">
+        <v>0.13760787599737026</v>
+      </c>
+      <c r="C59" s="0">
+        <v>3.6446766358104323</v>
+      </c>
+      <c r="D59" s="0">
+        <v>2.3718772700232038</v>
+      </c>
+      <c r="E59" s="0">
+        <v>0.0001260541559415388</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="0">
+        <v>0.35707181568030927</v>
+      </c>
+      <c r="B60" s="0">
+        <v>0.19997085517146868</v>
+      </c>
+      <c r="C60" s="0">
+        <v>3.6309218739053706</v>
+      </c>
+      <c r="D60" s="0">
+        <v>0.48236116714123412</v>
+      </c>
+      <c r="E60" s="0">
+        <v>0.00021037171677130105</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="0">
+        <v>0.65017069338484024</v>
+      </c>
+      <c r="B61" s="0">
+        <v>0.03795259397867945</v>
+      </c>
+      <c r="C61" s="0">
+        <v>1.5254458686945565</v>
+      </c>
+      <c r="D61" s="0">
+        <v>2.8295329284533683</v>
+      </c>
+      <c r="E61" s="0">
+        <v>7.8016228476967299e-06</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="0">
+        <v>0.47745393332032954</v>
+      </c>
+      <c r="B62" s="0">
+        <v>0.17978541546488491</v>
+      </c>
+      <c r="C62" s="0">
+        <v>1.5155880091949228</v>
+      </c>
+      <c r="D62" s="0">
+        <v>0.42934782264279681</v>
+      </c>
+      <c r="E62" s="0">
+        <v>0.00039888754215116387</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="0">
+        <v>0.99998049179964077</v>
+      </c>
+      <c r="B63" s="0">
+        <v>0.1989223620126474</v>
+      </c>
+      <c r="C63" s="0">
+        <v>2.1576782053168655</v>
+      </c>
+      <c r="D63" s="0">
+        <v>0.20428384497339472</v>
+      </c>
+      <c r="E63" s="0">
+        <v>0.0011222606493177666</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="0">
+        <v>0.51257716618278559</v>
+      </c>
+      <c r="B64" s="0">
+        <v>0.063478273229772009</v>
+      </c>
+      <c r="C64" s="0">
+        <v>1.5353695912387544</v>
+      </c>
+      <c r="D64" s="0">
+        <v>2.1219433836851893</v>
+      </c>
+      <c r="E64" s="0">
+        <v>4.4943707701499731e-05</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="0">
+        <v>0.83287470878863945</v>
+      </c>
+      <c r="B65" s="0">
+        <v>0.084325656365645096</v>
+      </c>
+      <c r="C65" s="0">
+        <v>1.5491860587526292</v>
+      </c>
+      <c r="D65" s="0">
+        <v>1.3703811818667497</v>
+      </c>
+      <c r="E65" s="0">
+        <v>0.00018580712253092575</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="0">
+        <v>0.99999999980594134</v>
+      </c>
+      <c r="B66" s="0">
+        <v>0.17404967199551355</v>
+      </c>
+      <c r="C66" s="0">
+        <v>1.4801776189727647</v>
+      </c>
+      <c r="D66" s="0">
+        <v>1.9577731705637573</v>
+      </c>
+      <c r="E66" s="0">
+        <v>0.028770831702728674</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="0">
+        <v>0.83343717247725169</v>
+      </c>
+      <c r="B67" s="0">
+        <v>0.19879911928964042</v>
+      </c>
+      <c r="C67" s="0">
+        <v>1.5536123377416979</v>
+      </c>
+      <c r="D67" s="0">
+        <v>1.8012169645044152</v>
+      </c>
+      <c r="E67" s="0">
+        <v>3.8826939767233783e-05</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="0">
+        <v>0.99999999999443379</v>
+      </c>
+      <c r="B68" s="0">
+        <v>0.11712056497488255</v>
+      </c>
+      <c r="C68" s="0">
+        <v>3.6358294184063906</v>
+      </c>
+      <c r="D68" s="0">
+        <v>0.31694637693293365</v>
+      </c>
+      <c r="E68" s="0">
+        <v>0.26755265613177009</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="0">
+        <v>0.49089035999384989</v>
+      </c>
+      <c r="B69" s="0">
+        <v>0.073893625151835493</v>
+      </c>
+      <c r="C69" s="0">
+        <v>3.6257746636554908</v>
+      </c>
+      <c r="D69" s="0">
+        <v>1.3420288520477224</v>
+      </c>
+      <c r="E69" s="0">
+        <v>1.2569238640533967e-05</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="0">
+        <v>0.99999996899325061</v>
+      </c>
+      <c r="B70" s="0">
+        <v>0.19715066376203361</v>
+      </c>
+      <c r="C70" s="0">
+        <v>3.6547292060188008</v>
+      </c>
+      <c r="D70" s="0">
+        <v>0.38452821507293083</v>
+      </c>
+      <c r="E70" s="0">
+        <v>0.007329161945404913</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="0">
+        <v>0.39475458766221871</v>
+      </c>
+      <c r="B71" s="0">
+        <v>0.1999951327651617</v>
+      </c>
+      <c r="C71" s="0">
+        <v>3.6603604533592655</v>
+      </c>
+      <c r="D71" s="0">
+        <v>0.61378375680377673</v>
+      </c>
+      <c r="E71" s="0">
+        <v>0.00092300863674713918</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="0">
+        <v>0.99999999726943067</v>
+      </c>
+      <c r="B72" s="0">
+        <v>0.16246205279480869</v>
+      </c>
+      <c r="C72" s="0">
+        <v>3.6190538677227573</v>
+      </c>
+      <c r="D72" s="0">
+        <v>2.6029006450983672</v>
+      </c>
+      <c r="E72" s="0">
+        <v>0.04189918074949732</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="0">
+        <v>0.87586780787665997</v>
+      </c>
+      <c r="B73" s="0">
+        <v>0.093400390749014225</v>
+      </c>
+      <c r="C73" s="0">
+        <v>3.6477921706370471</v>
+      </c>
+      <c r="D73" s="0">
+        <v>0.90056275600091829</v>
+      </c>
+      <c r="E73" s="0">
+        <v>0.00071950389640007854</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="0">
+        <v>0.51870839226264898</v>
+      </c>
+      <c r="B74" s="0">
+        <v>0.1554715616854643</v>
+      </c>
+      <c r="C74" s="0">
+        <v>3.635403536264564</v>
+      </c>
+      <c r="D74" s="0">
+        <v>2.1229319145550254</v>
+      </c>
+      <c r="E74" s="0">
+        <v>5.0578143983119809e-06</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="0">
+        <v>0.99999310443780631</v>
+      </c>
+      <c r="B75" s="0">
+        <v>0.12439186286151065</v>
+      </c>
+      <c r="C75" s="0">
+        <v>3.6355879532403166</v>
+      </c>
+      <c r="D75" s="0">
+        <v>2.8200399103325671</v>
+      </c>
+      <c r="E75" s="0">
+        <v>0.0010067101724480487</v>
       </c>
     </row>
   </sheetData>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -58,7 +58,7 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="true"/>
     <col min="2" max="2" width="13.7109375" customWidth="true"/>
-    <col min="3" max="3" width="11.7109375" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" customWidth="true"/>
     <col min="4" max="4" width="11.7109375" customWidth="true"/>
     <col min="5" max="5" width="12.7109375" customWidth="true"/>
     <col min="6" max="6" width="13.7109375" customWidth="true"/>
@@ -69,437 +69,437 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0">
-        <v>0.46494919406425178</v>
+        <v>0.76363365135228745</v>
       </c>
       <c r="B1" s="0">
-        <v>0.12939584928923337</v>
+        <v>0.08888519016512933</v>
       </c>
       <c r="C1" s="0">
-        <v>1.6190715077517868</v>
+        <v>1.5915908584895087</v>
       </c>
       <c r="D1" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E1" s="0">
-        <v>0.26409831164704506</v>
+        <v>0.43678569903044911</v>
       </c>
       <c r="F1" s="0">
-        <v>0.020009487707417728</v>
+        <v>0.024746642498929054</v>
       </c>
       <c r="G1" s="0">
-        <v>3.3050218707657288</v>
+        <v>4.0522915968346922</v>
       </c>
       <c r="H1" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I1" s="0">
-        <v>5.5579083927524182e-06</v>
+        <v>1.0218740945602944e-08</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>0.45295586893178053</v>
+        <v>0.2361928483768298</v>
       </c>
       <c r="B2" s="0">
-        <v>0.08336256272682778</v>
+        <v>0.12963296786042683</v>
       </c>
       <c r="C2" s="0">
-        <v>1.5780252517185653</v>
+        <v>1.6532551903303669</v>
       </c>
       <c r="D2" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E2" s="0">
-        <v>0.64275082172063169</v>
+        <v>0.42307346571120047</v>
       </c>
       <c r="F2" s="0">
-        <v>0.024290449442103752</v>
+        <v>0.020000017626560177</v>
       </c>
       <c r="G2" s="0">
-        <v>4.6985016730305746</v>
+        <v>4.7519267340730167</v>
       </c>
       <c r="H2" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I2" s="0">
-        <v>3.7486559566318778e-06</v>
+        <v>1.9019607825814942e-07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.94551212918129546</v>
+        <v>0.75817542182106845</v>
       </c>
       <c r="B3" s="0">
-        <v>0.17370533462932519</v>
+        <v>0.18070210151059904</v>
       </c>
       <c r="C3" s="0">
-        <v>1.60053519576169</v>
+        <v>1.6018341710038033</v>
       </c>
       <c r="D3" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E3" s="0">
-        <v>0.45037434758236827</v>
+        <v>0.30463689776690051</v>
       </c>
       <c r="F3" s="0">
-        <v>0.081459899529797444</v>
+        <v>0.032462969578982204</v>
       </c>
       <c r="G3" s="0">
-        <v>4.7635012537812669</v>
+        <v>4.779461427088977</v>
       </c>
       <c r="H3" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I3" s="0">
-        <v>1.8978163258711729e-05</v>
+        <v>2.192318654833206e-07</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.30138395208062263</v>
+        <v>0.52721599036919065</v>
       </c>
       <c r="B4" s="0">
-        <v>0.19705670406443784</v>
+        <v>0.13064266340979669</v>
       </c>
       <c r="C4" s="0">
-        <v>1.4640146948999122</v>
+        <v>1.5692194584815133</v>
       </c>
       <c r="D4" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E4" s="0">
-        <v>0.71824829865091189</v>
+        <v>0.77627959066504493</v>
       </c>
       <c r="F4" s="0">
-        <v>0.051420659106028721</v>
+        <v>0.04483867146613775</v>
       </c>
       <c r="G4" s="0">
-        <v>3.3402763911202342</v>
+        <v>3.6594988321543296</v>
       </c>
       <c r="H4" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I4" s="0">
-        <v>6.9264733304223934e-06</v>
+        <v>6.96360561720752e-08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.52289293380125046</v>
+        <v>0.60713301008119613</v>
       </c>
       <c r="B5" s="0">
-        <v>0.09683808059827928</v>
+        <v>0.090858055647504404</v>
       </c>
       <c r="C5" s="0">
-        <v>3.4082518802200492</v>
+        <v>2.9813250275329457</v>
       </c>
       <c r="D5" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E5" s="0">
-        <v>0.53361402151263604</v>
+        <v>0.66459208617919552</v>
       </c>
       <c r="F5" s="0">
-        <v>0.08125767348174448</v>
+        <v>0.086605784603893468</v>
       </c>
       <c r="G5" s="0">
-        <v>3.8731405691951282</v>
+        <v>4.2368231284953302</v>
       </c>
       <c r="H5" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I5" s="0">
-        <v>6.1657186592090775e-06</v>
+        <v>2.7453203073212905e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.22585846929220876</v>
+        <v>0.8144252781731437</v>
       </c>
       <c r="B6" s="0">
-        <v>0.14652385779443095</v>
+        <v>0.096125258969866748</v>
       </c>
       <c r="C6" s="0">
-        <v>2.8694937721604359</v>
+        <v>2.8815087289782082</v>
       </c>
       <c r="D6" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E6" s="0">
-        <v>0.91536177013515352</v>
+        <v>0.52750015746723689</v>
       </c>
       <c r="F6" s="0">
-        <v>0.076147256897794321</v>
+        <v>0.074228373720110985</v>
       </c>
       <c r="G6" s="0">
-        <v>3.4535909824894375</v>
+        <v>4.1023158331038303</v>
       </c>
       <c r="H6" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I6" s="0">
-        <v>3.0325798590758987e-06</v>
+        <v>3.7668415371455878e-07</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>0.58036382003897147</v>
+        <v>0.64637441469415347</v>
       </c>
       <c r="B7" s="0">
-        <v>0.14532857187416842</v>
+        <v>0.12953535920944981</v>
       </c>
       <c r="C7" s="0">
-        <v>3.2124008455685962</v>
+        <v>2.8837153646999623</v>
       </c>
       <c r="D7" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E7" s="0">
-        <v>0.56646971235920485</v>
+        <v>0.68389247067324233</v>
       </c>
       <c r="F7" s="0">
-        <v>0.086797073278955209</v>
+        <v>0.1043476293615514</v>
       </c>
       <c r="G7" s="0">
-        <v>3.8118639621024735</v>
+        <v>4.0916041799748522</v>
       </c>
       <c r="H7" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I7" s="0">
-        <v>2.5724568438911729e-06</v>
+        <v>9.2540084858739116e-07</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>0.71638030975061862</v>
+        <v>0.77057969060101694</v>
       </c>
       <c r="B8" s="0">
-        <v>0.14350431964412669</v>
+        <v>0.13106213675642675</v>
       </c>
       <c r="C8" s="0">
-        <v>3.1358170417740201</v>
+        <v>2.8258416527406154</v>
       </c>
       <c r="D8" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E8" s="0">
-        <v>0.4681031435348918</v>
+        <v>0.63701334027023304</v>
       </c>
       <c r="F8" s="0">
-        <v>0.076234715125892763</v>
+        <v>0.099807208834126471</v>
       </c>
       <c r="G8" s="0">
-        <v>3.8492952607801145</v>
+        <v>4.1514962125184747</v>
       </c>
       <c r="H8" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I8" s="0">
-        <v>5.0031203443924436e-06</v>
+        <v>9.7908619354922661e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>0.39115139394893778</v>
+        <v>0.26678114285968224</v>
       </c>
       <c r="B9" s="0">
-        <v>0.17848613232598826</v>
+        <v>0.18110205090970105</v>
       </c>
       <c r="C9" s="0">
-        <v>3.1553352325056365</v>
+        <v>2.4156391455236372</v>
       </c>
       <c r="D9" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E9" s="0">
-        <v>0.3376916900981245</v>
+        <v>0.5941161585705077</v>
       </c>
       <c r="F9" s="0">
-        <v>0.026753075845865247</v>
+        <v>0.093832982205083446</v>
       </c>
       <c r="G9" s="0">
-        <v>3.8761623796876643</v>
+        <v>3.9005298078518709</v>
       </c>
       <c r="H9" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I9" s="0">
-        <v>3.0215967247152278e-06</v>
+        <v>6.1997032788828846e-07</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>0.95500777035355255</v>
+        <v>0.97831711335596638</v>
       </c>
       <c r="B10" s="0">
-        <v>0.16187131340355476</v>
+        <v>0.15277152791140047</v>
       </c>
       <c r="C10" s="0">
-        <v>3.2004098840767701</v>
+        <v>3.0942799368390244</v>
       </c>
       <c r="D10" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E10" s="0">
-        <v>0.56929918428276849</v>
+        <v>0.60983392468265252</v>
       </c>
       <c r="F10" s="0">
-        <v>0.038310976199279478</v>
+        <v>0.060676688669076488</v>
       </c>
       <c r="G10" s="0">
-        <v>3.9543421549541562</v>
+        <v>4.1349589044002881</v>
       </c>
       <c r="H10" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I10" s="0">
-        <v>1.3946083844033257e-05</v>
+        <v>1.4352086796852891e-06</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>0.22895453303777191</v>
+        <v>0.17620896176457868</v>
       </c>
       <c r="B11" s="0">
-        <v>0.092425680402638849</v>
+        <v>0.099286257032007066</v>
       </c>
       <c r="C11" s="0">
-        <v>1.9435175511633407</v>
+        <v>0.12186637325268596</v>
       </c>
       <c r="D11" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E11" s="0">
-        <v>0.80200266584895874</v>
+        <v>0.65619757764419362</v>
       </c>
       <c r="F11" s="0">
-        <v>0.090845807363278352</v>
+        <v>0.088113330033240705</v>
       </c>
       <c r="G11" s="0">
-        <v>4.7613997274183504</v>
+        <v>4.3571793173094253</v>
       </c>
       <c r="H11" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I11" s="0">
-        <v>4.5058826258141946e-06</v>
+        <v>8.7905820271715823e-08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>0.90114115674254114</v>
+        <v>0.95728856181666944</v>
       </c>
       <c r="B12" s="0">
-        <v>0.12212369847926889</v>
+        <v>0.11629478017871611</v>
       </c>
       <c r="C12" s="0">
-        <v>4.7879032099079879</v>
+        <v>4.6704620216669444</v>
       </c>
       <c r="D12" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E12" s="0">
-        <v>0.77076018971583138</v>
+        <v>0.66378324995961235</v>
       </c>
       <c r="F12" s="0">
-        <v>0.033442190427954335</v>
+        <v>0.020010429330519604</v>
       </c>
       <c r="G12" s="0">
-        <v>3.1657457889830156</v>
+        <v>3.0768212349740671</v>
       </c>
       <c r="H12" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I12" s="0">
-        <v>5.2721899592441147e-06</v>
+        <v>4.2614175506698193e-07</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>0.39029559980793083</v>
+        <v>0.69971262479204777</v>
       </c>
       <c r="B13" s="0">
-        <v>0.17939657912288887</v>
+        <v>0.11556320577332801</v>
       </c>
       <c r="C13" s="0">
-        <v>4.77524333088909</v>
+        <v>4.415148212454814</v>
       </c>
       <c r="D13" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E13" s="0">
-        <v>0.52073102586095477</v>
+        <v>0.40924275139356486</v>
       </c>
       <c r="F13" s="0">
-        <v>0.066167145645490449</v>
+        <v>0.020993314529002112</v>
       </c>
       <c r="G13" s="0">
-        <v>3.1652411388562318</v>
+        <v>2.3753136829666475</v>
       </c>
       <c r="H13" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I13" s="0">
-        <v>4.1341226486663472e-06</v>
+        <v>3.8088550880511999e-07</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>0.5319492699732804</v>
+        <v>0.62762904706019684</v>
       </c>
       <c r="B14" s="0">
-        <v>0.17760176561114949</v>
+        <v>0.15592001226964788</v>
       </c>
       <c r="C14" s="0">
-        <v>4.6376371378789347</v>
+        <v>4.6658380803727662</v>
       </c>
       <c r="D14" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E14" s="0">
-        <v>0.55991927009066922</v>
+        <v>0.44377945999398916</v>
       </c>
       <c r="F14" s="0">
-        <v>0.020000000000022205</v>
+        <v>0.020084377410258255</v>
       </c>
       <c r="G14" s="0">
-        <v>4.7214665516405248</v>
+        <v>4.674487308102333</v>
       </c>
       <c r="H14" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I14" s="0">
-        <v>1.8974768311189834e-05</v>
+        <v>2.9722812632829164e-06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>0.83087101699627564</v>
+        <v>0.80051743502710881</v>
       </c>
       <c r="B15" s="0">
-        <v>0.19999999907274948</v>
+        <v>0.19812384042746445</v>
       </c>
       <c r="C15" s="0">
-        <v>4.8776022155051351</v>
+        <v>4.742777937040966</v>
       </c>
       <c r="D15" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E15" s="0">
-        <v>0.44112636588224152</v>
+        <v>0.34005316031621635</v>
       </c>
       <c r="F15" s="0">
-        <v>0.1239764204895776</v>
+        <v>0.098623373038771583</v>
       </c>
       <c r="G15" s="0">
-        <v>2.7203547064393145</v>
+        <v>2.6164806530645572</v>
       </c>
       <c r="H15" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I15" s="0">
-        <v>2.5288064699482858e-05</v>
+        <v>2.1845103513639877e-07</v>
       </c>
     </row>
   </sheetData>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -58,7 +58,7 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="true"/>
     <col min="2" max="2" width="13.7109375" customWidth="true"/>
-    <col min="3" max="3" width="12.7109375" customWidth="true"/>
+    <col min="3" max="3" width="11.7109375" customWidth="true"/>
     <col min="4" max="4" width="11.7109375" customWidth="true"/>
     <col min="5" max="5" width="12.7109375" customWidth="true"/>
     <col min="6" max="6" width="13.7109375" customWidth="true"/>
@@ -69,437 +69,437 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0">
-        <v>0.76363365135228745</v>
+        <v>0.36812589768930226</v>
       </c>
       <c r="B1" s="0">
-        <v>0.08888519016512933</v>
+        <v>0.15632348649605163</v>
       </c>
       <c r="C1" s="0">
-        <v>1.5915908584895087</v>
+        <v>1.529531460180177</v>
       </c>
       <c r="D1" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E1" s="0">
-        <v>0.43678569903044911</v>
+        <v>0.30024142250950914</v>
       </c>
       <c r="F1" s="0">
-        <v>0.024746642498929054</v>
+        <v>0.03101431493391834</v>
       </c>
       <c r="G1" s="0">
-        <v>4.0522915968346922</v>
+        <v>3.1262104863074311</v>
       </c>
       <c r="H1" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I1" s="0">
-        <v>1.0218740945602944e-08</v>
+        <v>1.3240492512382839e-06</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>0.2361928483768298</v>
+        <v>0.56004930068563363</v>
       </c>
       <c r="B2" s="0">
-        <v>0.12963296786042683</v>
+        <v>0.16686693714739556</v>
       </c>
       <c r="C2" s="0">
-        <v>1.6532551903303669</v>
+        <v>1.534819317952397</v>
       </c>
       <c r="D2" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E2" s="0">
-        <v>0.42307346571120047</v>
+        <v>0.68274928290561365</v>
       </c>
       <c r="F2" s="0">
-        <v>0.020000017626560177</v>
+        <v>0.094720719090467115</v>
       </c>
       <c r="G2" s="0">
-        <v>4.7519267340730167</v>
+        <v>4.6774162642617716</v>
       </c>
       <c r="H2" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I2" s="0">
-        <v>1.9019607825814942e-07</v>
+        <v>7.6862678292148174e-06</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.75817542182106845</v>
+        <v>0.85920177522492991</v>
       </c>
       <c r="B3" s="0">
-        <v>0.18070210151059904</v>
+        <v>0.18519334189436665</v>
       </c>
       <c r="C3" s="0">
-        <v>1.6018341710038033</v>
+        <v>1.6012035230502721</v>
       </c>
       <c r="D3" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E3" s="0">
-        <v>0.30463689776690051</v>
+        <v>0.47344361257026446</v>
       </c>
       <c r="F3" s="0">
-        <v>0.032462969578982204</v>
+        <v>0.10687620803731127</v>
       </c>
       <c r="G3" s="0">
-        <v>4.779461427088977</v>
+        <v>4.8430913984623603</v>
       </c>
       <c r="H3" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I3" s="0">
-        <v>2.192318654833206e-07</v>
+        <v>1.3311327359854187e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.52721599036919065</v>
+        <v>0.29978582893680189</v>
       </c>
       <c r="B4" s="0">
-        <v>0.13064266340979669</v>
+        <v>0.19980744544364126</v>
       </c>
       <c r="C4" s="0">
-        <v>1.5692194584815133</v>
+        <v>1.4734900722218307</v>
       </c>
       <c r="D4" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E4" s="0">
-        <v>0.77627959066504493</v>
+        <v>0.72588706707290052</v>
       </c>
       <c r="F4" s="0">
-        <v>0.04483867146613775</v>
+        <v>0.049748908514736456</v>
       </c>
       <c r="G4" s="0">
-        <v>3.6594988321543296</v>
+        <v>3.4079606035096717</v>
       </c>
       <c r="H4" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I4" s="0">
-        <v>6.96360561720752e-08</v>
+        <v>3.4862002203800943e-06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.60713301008119613</v>
+        <v>0.6806331994574889</v>
       </c>
       <c r="B5" s="0">
-        <v>0.090858055647504404</v>
+        <v>0.086026430432652817</v>
       </c>
       <c r="C5" s="0">
-        <v>2.9813250275329457</v>
+        <v>2.9409907946849319</v>
       </c>
       <c r="D5" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E5" s="0">
-        <v>0.66459208617919552</v>
+        <v>0.67901010121903682</v>
       </c>
       <c r="F5" s="0">
-        <v>0.086605784603893468</v>
+        <v>0.080471232759914829</v>
       </c>
       <c r="G5" s="0">
-        <v>4.2368231284953302</v>
+        <v>4.4003431901341186</v>
       </c>
       <c r="H5" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I5" s="0">
-        <v>2.7453203073212905e-06</v>
+        <v>8.1464082771986257e-06</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.8144252781731437</v>
+        <v>0.77393892308662438</v>
       </c>
       <c r="B6" s="0">
-        <v>0.096125258969866748</v>
+        <v>0.082857599157317233</v>
       </c>
       <c r="C6" s="0">
-        <v>2.8815087289782082</v>
+        <v>3.1045395242461655</v>
       </c>
       <c r="D6" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E6" s="0">
-        <v>0.52750015746723689</v>
+        <v>0.43045698478271283</v>
       </c>
       <c r="F6" s="0">
-        <v>0.074228373720110985</v>
+        <v>0.048545751751218176</v>
       </c>
       <c r="G6" s="0">
-        <v>4.1023158331038303</v>
+        <v>3.8935493864284476</v>
       </c>
       <c r="H6" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I6" s="0">
-        <v>3.7668415371455878e-07</v>
+        <v>1.9358100401641475e-05</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>0.64637441469415347</v>
+        <v>0.24090802440847459</v>
       </c>
       <c r="B7" s="0">
-        <v>0.12953535920944981</v>
+        <v>0.15326383679369923</v>
       </c>
       <c r="C7" s="0">
-        <v>2.8837153646999623</v>
+        <v>2.867759016008355</v>
       </c>
       <c r="D7" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E7" s="0">
-        <v>0.68389247067324233</v>
+        <v>0.92856669670630876</v>
       </c>
       <c r="F7" s="0">
-        <v>0.1043476293615514</v>
+        <v>0.085631391217949729</v>
       </c>
       <c r="G7" s="0">
-        <v>4.0916041799748522</v>
+        <v>3.6422948784847131</v>
       </c>
       <c r="H7" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I7" s="0">
-        <v>9.2540084858739116e-07</v>
+        <v>1.706338825363683e-05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>0.77057969060101694</v>
+        <v>0.69162729491676089</v>
       </c>
       <c r="B8" s="0">
-        <v>0.13106213675642675</v>
+        <v>0.11092201197710488</v>
       </c>
       <c r="C8" s="0">
-        <v>2.8258416527406154</v>
+        <v>3.0127857942366614</v>
       </c>
       <c r="D8" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E8" s="0">
-        <v>0.63701334027023304</v>
+        <v>0.73867832090078001</v>
       </c>
       <c r="F8" s="0">
-        <v>0.099807208834126471</v>
+        <v>0.065091239748481869</v>
       </c>
       <c r="G8" s="0">
-        <v>4.1514962125184747</v>
+        <v>3.8151842033432355</v>
       </c>
       <c r="H8" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I8" s="0">
-        <v>9.7908619354922661e-07</v>
+        <v>4.2574098699885561e-05</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>0.26678114285968224</v>
+        <v>0.44227332682612736</v>
       </c>
       <c r="B9" s="0">
-        <v>0.18110205090970105</v>
+        <v>0.18485320333525496</v>
       </c>
       <c r="C9" s="0">
-        <v>2.4156391455236372</v>
+        <v>3.1601558205378004</v>
       </c>
       <c r="D9" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E9" s="0">
-        <v>0.5941161585705077</v>
+        <v>0.32131769996080994</v>
       </c>
       <c r="F9" s="0">
-        <v>0.093832982205083446</v>
+        <v>0.027491822674676578</v>
       </c>
       <c r="G9" s="0">
-        <v>3.9005298078518709</v>
+        <v>4.0307143013635649</v>
       </c>
       <c r="H9" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I9" s="0">
-        <v>6.1997032788828846e-07</v>
+        <v>3.7671144603751207e-06</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>0.97831711335596638</v>
+        <v>0.35705684567240348</v>
       </c>
       <c r="B10" s="0">
-        <v>0.15277152791140047</v>
+        <v>0.16128237383631006</v>
       </c>
       <c r="C10" s="0">
-        <v>3.0942799368390244</v>
+        <v>1.5220114176391086</v>
       </c>
       <c r="D10" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E10" s="0">
-        <v>0.60983392468265252</v>
+        <v>0.30503872897248818</v>
       </c>
       <c r="F10" s="0">
-        <v>0.060676688669076488</v>
+        <v>0.031805446057841115</v>
       </c>
       <c r="G10" s="0">
-        <v>4.1349589044002881</v>
+        <v>3.1029548174512036</v>
       </c>
       <c r="H10" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I10" s="0">
-        <v>1.4352086796852891e-06</v>
+        <v>2.0123723052764442e-06</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0">
-        <v>0.17620896176457868</v>
+        <v>0.38361274929049743</v>
       </c>
       <c r="B11" s="0">
-        <v>0.099286257032007066</v>
+        <v>0.11941426198311951</v>
       </c>
       <c r="C11" s="0">
-        <v>0.12186637325268596</v>
+        <v>4.6791184330747715</v>
       </c>
       <c r="D11" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E11" s="0">
-        <v>0.65619757764419362</v>
+        <v>0.16441798445049088</v>
       </c>
       <c r="F11" s="0">
-        <v>0.088113330033240705</v>
+        <v>0.023999915201576027</v>
       </c>
       <c r="G11" s="0">
-        <v>4.3571793173094253</v>
+        <v>4.3756608637894479</v>
       </c>
       <c r="H11" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I11" s="0">
-        <v>8.7905820271715823e-08</v>
+        <v>9.9352468816000884e-07</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0">
-        <v>0.95728856181666944</v>
+        <v>0.57884488557674163</v>
       </c>
       <c r="B12" s="0">
-        <v>0.11629478017871611</v>
+        <v>0.1342860126946413</v>
       </c>
       <c r="C12" s="0">
-        <v>4.6704620216669444</v>
+        <v>4.8180208803924716</v>
       </c>
       <c r="D12" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E12" s="0">
-        <v>0.66378324995961235</v>
+        <v>0.9055598607527191</v>
       </c>
       <c r="F12" s="0">
-        <v>0.020010429330519604</v>
+        <v>0.027514195310973343</v>
       </c>
       <c r="G12" s="0">
-        <v>3.0768212349740671</v>
+        <v>3.6914931016924668</v>
       </c>
       <c r="H12" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I12" s="0">
-        <v>4.2614175506698193e-07</v>
+        <v>3.758143940003182e-05</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0">
-        <v>0.69971262479204777</v>
+        <v>0.36903295678703757</v>
       </c>
       <c r="B13" s="0">
-        <v>0.11556320577332801</v>
+        <v>0.19896050699611009</v>
       </c>
       <c r="C13" s="0">
-        <v>4.415148212454814</v>
+        <v>4.8428322746841319</v>
       </c>
       <c r="D13" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E13" s="0">
-        <v>0.40924275139356486</v>
+        <v>0.52304822935629181</v>
       </c>
       <c r="F13" s="0">
-        <v>0.020993314529002112</v>
+        <v>0.072909479066983626</v>
       </c>
       <c r="G13" s="0">
-        <v>2.3753136829666475</v>
+        <v>3.166876271307697</v>
       </c>
       <c r="H13" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I13" s="0">
-        <v>3.8088550880511999e-07</v>
+        <v>3.9443999910919594e-06</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="0">
-        <v>0.62762904706019684</v>
+        <v>0.50248823188162883</v>
       </c>
       <c r="B14" s="0">
-        <v>0.15592001226964788</v>
+        <v>0.19691519977181102</v>
       </c>
       <c r="C14" s="0">
-        <v>4.6658380803727662</v>
+        <v>4.6703707719310534</v>
       </c>
       <c r="D14" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E14" s="0">
-        <v>0.44377945999398916</v>
+        <v>0.65787117500335124</v>
       </c>
       <c r="F14" s="0">
-        <v>0.020084377410258255</v>
+        <v>0.020000000000022205</v>
       </c>
       <c r="G14" s="0">
-        <v>4.674487308102333</v>
+        <v>4.4666205933662537</v>
       </c>
       <c r="H14" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I14" s="0">
-        <v>2.9722812632829164e-06</v>
+        <v>2.3669180565077491e-05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="0">
-        <v>0.80051743502710881</v>
+        <v>0.3610082897573525</v>
       </c>
       <c r="B15" s="0">
-        <v>0.19812384042746445</v>
+        <v>0.16094511301474176</v>
       </c>
       <c r="C15" s="0">
-        <v>4.742777937040966</v>
+        <v>1.5261251170999763</v>
       </c>
       <c r="D15" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="E15" s="0">
-        <v>0.34005316031621635</v>
+        <v>0.30531802559027493</v>
       </c>
       <c r="F15" s="0">
-        <v>0.098623373038771583</v>
+        <v>0.030761094875371597</v>
       </c>
       <c r="G15" s="0">
-        <v>2.6164806530645572</v>
+        <v>3.1338443156560567</v>
       </c>
       <c r="H15" s="0">
         <v>1.5707963267948966</v>
       </c>
       <c r="I15" s="0">
-        <v>2.1845103513639877e-07</v>
+        <v>3.0803365020261157e-06</v>
       </c>
     </row>
   </sheetData>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -59,147 +59,147 @@
     <col min="1" max="1" width="12.7109375" customWidth="true"/>
     <col min="2" max="2" width="13.7109375" customWidth="true"/>
     <col min="3" max="3" width="11.7109375" customWidth="true"/>
-    <col min="4" max="4" width="15.5703125" customWidth="true"/>
+    <col min="4" max="4" width="15.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0">
-        <v>0.32075782814524645</v>
+        <v>0.40202965392158824</v>
       </c>
       <c r="B1" s="0">
-        <v>0.074003821461399819</v>
+        <v>0.069789383849933759</v>
       </c>
       <c r="C1" s="0">
-        <v>1.5853023231065195</v>
+        <v>1.58612318996072</v>
       </c>
       <c r="D1" s="0">
-        <v>2.6149565217337974e-06</v>
+        <v>0.00016932000391698518</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>0.69921487566029394</v>
+        <v>0.75713708359141785</v>
       </c>
       <c r="B2" s="0">
-        <v>0.073995548260789301</v>
+        <v>0.072421632945224593</v>
       </c>
       <c r="C2" s="0">
-        <v>1.5911625880769449</v>
+        <v>1.5945817689101296</v>
       </c>
       <c r="D2" s="0">
-        <v>5.8117385846313961e-06</v>
+        <v>0.00047490785077414997</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.28895388073080225</v>
+        <v>0.27154159433860381</v>
       </c>
       <c r="B3" s="0">
-        <v>0.0742178397549874</v>
+        <v>0.087965747246715797</v>
       </c>
       <c r="C3" s="0">
-        <v>1.5831417167977364</v>
+        <v>1.5813627191821027</v>
       </c>
       <c r="D3" s="0">
-        <v>1.4716480697429027e-07</v>
+        <v>2.4160611469808265e-05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.45239181112799459</v>
+        <v>0.47465787170457124</v>
       </c>
       <c r="B4" s="0">
-        <v>0.11835714043821086</v>
+        <v>0.11103571411521253</v>
       </c>
       <c r="C4" s="0">
-        <v>1.5823273711878392</v>
+        <v>1.5881187616702976</v>
       </c>
       <c r="D4" s="0">
-        <v>4.4460841505104192e-08</v>
+        <v>3.7665609979489553e-05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.63538728943542566</v>
+        <v>0.69137551224771843</v>
       </c>
       <c r="B5" s="0">
-        <v>0.11895320824093356</v>
+        <v>0.11069471761559577</v>
       </c>
       <c r="C5" s="0">
-        <v>1.5896242439450536</v>
+        <v>1.587425379177277</v>
       </c>
       <c r="D5" s="0">
-        <v>2.239848024433164e-07</v>
+        <v>3.0100158065422581e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.84373582880360964</v>
+        <v>0.37550210442667975</v>
       </c>
       <c r="B6" s="0">
-        <v>0.075210384964515486</v>
+        <v>0.17311447561668428</v>
       </c>
       <c r="C6" s="0">
-        <v>1.5866905529363664</v>
+        <v>1.5796254680421602</v>
       </c>
       <c r="D6" s="0">
-        <v>4.1836825054186623e-08</v>
+        <v>0.00021109742122939963</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>0.71228991536580089</v>
+        <v>0.56497426045613874</v>
       </c>
       <c r="B7" s="0">
-        <v>0.14679797709367529</v>
+        <v>0.16528493275999942</v>
       </c>
       <c r="C7" s="0">
-        <v>1.5845757713540167</v>
+        <v>1.580299241084306</v>
       </c>
       <c r="D7" s="0">
-        <v>7.1171167032728378e-12</v>
+        <v>0.00031827266330454809</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>0.86927639088459607</v>
+        <v>0.83481970399375527</v>
       </c>
       <c r="B8" s="0">
-        <v>0.15651368335008145</v>
+        <v>0.16829695270786463</v>
       </c>
       <c r="C8" s="0">
-        <v>1.6025043966658039</v>
+        <v>1.5875321449709592</v>
       </c>
       <c r="D8" s="0">
-        <v>3.6548770322275363e-07</v>
+        <v>0.00026277613828493574</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0">
-        <v>0.45012259222037515</v>
+        <v>0.30032903077135142</v>
       </c>
       <c r="B9" s="0">
-        <v>0.11838761637842996</v>
+        <v>0.19999999998884047</v>
       </c>
       <c r="C9" s="0">
-        <v>1.5848803534284217</v>
+        <v>1.577600833859351</v>
       </c>
       <c r="D9" s="0">
-        <v>2.5820283031320087e-06</v>
+        <v>0.00057301024997264923</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0">
-        <v>0.83775405388471647</v>
+        <v>0.6627908436895753</v>
       </c>
       <c r="B10" s="0">
-        <v>0.15640526177146394</v>
+        <v>0.178739938276433</v>
       </c>
       <c r="C10" s="0">
-        <v>1.59136078034149</v>
+        <v>1.5816122798542704</v>
       </c>
       <c r="D10" s="0">
-        <v>1.8885842966200743e-06</v>
+        <v>0.00028685918484907337</v>
       </c>
     </row>
   </sheetData>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -53,153 +53,97 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="true"/>
-    <col min="2" max="2" width="13.7109375" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" customWidth="true"/>
     <col min="3" max="3" width="11.7109375" customWidth="true"/>
-    <col min="4" max="4" width="15.7109375" customWidth="true"/>
+    <col min="4" max="4" width="14.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0">
-        <v>0.40202965392158824</v>
+        <v>0.68297026231905456</v>
       </c>
       <c r="B1" s="0">
-        <v>0.069789383849933759</v>
+        <v>0.13933140088115567</v>
       </c>
       <c r="C1" s="0">
-        <v>1.58612318996072</v>
+        <v>1.5866582432652172</v>
       </c>
       <c r="D1" s="0">
-        <v>0.00016932000391698518</v>
+        <v>0.0015167950364546642</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>0.75713708359141785</v>
+        <v>0.40640589156575424</v>
       </c>
       <c r="B2" s="0">
-        <v>0.072421632945224593</v>
+        <v>0.19999999999995946</v>
       </c>
       <c r="C2" s="0">
-        <v>1.5945817689101296</v>
+        <v>1.5811910258947344</v>
       </c>
       <c r="D2" s="0">
-        <v>0.00047490785077414997</v>
+        <v>0.033214077866668329</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.27154159433860381</v>
+        <v>0.62327999688776803</v>
       </c>
       <c r="B3" s="0">
-        <v>0.087965747246715797</v>
+        <v>0.19180256885610766</v>
       </c>
       <c r="C3" s="0">
-        <v>1.5813627191821027</v>
+        <v>1.5791817036747455</v>
       </c>
       <c r="D3" s="0">
-        <v>2.4160611469808265e-05</v>
+        <v>0.010687967136026393</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.47465787170457124</v>
+        <v>0.75041769408300663</v>
       </c>
       <c r="B4" s="0">
-        <v>0.11103571411521253</v>
+        <v>0.14059847501826422</v>
       </c>
       <c r="C4" s="0">
-        <v>1.5881187616702976</v>
+        <v>1.5452699186482521</v>
       </c>
       <c r="D4" s="0">
-        <v>3.7665609979489553e-05</v>
+        <v>0.0063608251062703151</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.69137551224771843</v>
+        <v>0.3727073209734087</v>
       </c>
       <c r="B5" s="0">
-        <v>0.11069471761559577</v>
+        <v>0.19999999999952101</v>
       </c>
       <c r="C5" s="0">
-        <v>1.587425379177277</v>
+        <v>1.5905315247833587</v>
       </c>
       <c r="D5" s="0">
-        <v>3.0100158065422581e-05</v>
+        <v>0.052515857632866779</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.37550210442667975</v>
+        <v>0.688462474755833</v>
       </c>
       <c r="B6" s="0">
-        <v>0.17311447561668428</v>
+        <v>0.19463226266036848</v>
       </c>
       <c r="C6" s="0">
-        <v>1.5796254680421602</v>
+        <v>1.5829230892441168</v>
       </c>
       <c r="D6" s="0">
-        <v>0.00021109742122939963</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0">
-        <v>0.56497426045613874</v>
-      </c>
-      <c r="B7" s="0">
-        <v>0.16528493275999942</v>
-      </c>
-      <c r="C7" s="0">
-        <v>1.580299241084306</v>
-      </c>
-      <c r="D7" s="0">
-        <v>0.00031827266330454809</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0">
-        <v>0.83481970399375527</v>
-      </c>
-      <c r="B8" s="0">
-        <v>0.16829695270786463</v>
-      </c>
-      <c r="C8" s="0">
-        <v>1.5875321449709592</v>
-      </c>
-      <c r="D8" s="0">
-        <v>0.00026277613828493574</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0">
-        <v>0.30032903077135142</v>
-      </c>
-      <c r="B9" s="0">
-        <v>0.19999999998884047</v>
-      </c>
-      <c r="C9" s="0">
-        <v>1.577600833859351</v>
-      </c>
-      <c r="D9" s="0">
-        <v>0.00057301024997264923</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0">
-        <v>0.6627908436895753</v>
-      </c>
-      <c r="B10" s="0">
-        <v>0.178739938276433</v>
-      </c>
-      <c r="C10" s="0">
-        <v>1.5816122798542704</v>
-      </c>
-      <c r="D10" s="0">
-        <v>0.00028685918484907337</v>
+        <v>0.016370899689140885</v>
       </c>
     </row>
   </sheetData>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -53,97 +53,153 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="true"/>
-    <col min="2" max="2" width="12.7109375" customWidth="true"/>
+    <col min="2" max="2" width="13.7109375" customWidth="true"/>
     <col min="3" max="3" width="11.7109375" customWidth="true"/>
-    <col min="4" max="4" width="14.7109375" customWidth="true"/>
+    <col min="4" max="4" width="15.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0">
-        <v>0.68297026231905456</v>
+        <v>0.33376862047222772</v>
       </c>
       <c r="B1" s="0">
-        <v>0.13933140088115567</v>
+        <v>0.028419780335263316</v>
       </c>
       <c r="C1" s="0">
-        <v>1.5866582432652172</v>
+        <v>1.5886060698980584</v>
       </c>
       <c r="D1" s="0">
-        <v>0.0015167950364546642</v>
+        <v>0.00089436556506111123</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>0.40640589156575424</v>
+        <v>0.3555142389497456</v>
       </c>
       <c r="B2" s="0">
-        <v>0.19999999999995946</v>
+        <v>0.025867121052302759</v>
       </c>
       <c r="C2" s="0">
-        <v>1.5811910258947344</v>
+        <v>1.5998231828576677</v>
       </c>
       <c r="D2" s="0">
-        <v>0.033214077866668329</v>
+        <v>0.0047206779890769154</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.62327999688776803</v>
+        <v>0.6878218073941077</v>
       </c>
       <c r="B3" s="0">
-        <v>0.19180256885610766</v>
+        <v>0.034125252229147376</v>
       </c>
       <c r="C3" s="0">
-        <v>1.5791817036747455</v>
+        <v>1.5794913011571994</v>
       </c>
       <c r="D3" s="0">
-        <v>0.010687967136026393</v>
+        <v>0.00017308635482584788</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.75041769408300663</v>
+        <v>0.82615525908195564</v>
       </c>
       <c r="B4" s="0">
-        <v>0.14059847501826422</v>
+        <v>0.069401042863820414</v>
       </c>
       <c r="C4" s="0">
-        <v>1.5452699186482521</v>
+        <v>1.5919747898389367</v>
       </c>
       <c r="D4" s="0">
-        <v>0.0063608251062703151</v>
+        <v>0.0010618026526831288</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.3727073209734087</v>
+        <v>0.69615947991023996</v>
       </c>
       <c r="B5" s="0">
-        <v>0.19999999999952101</v>
+        <v>0.10071391548769121</v>
       </c>
       <c r="C5" s="0">
-        <v>1.5905315247833587</v>
+        <v>1.5905381284842586</v>
       </c>
       <c r="D5" s="0">
-        <v>0.052515857632866779</v>
+        <v>0.0039969747079750652</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.688462474755833</v>
+        <v>0.51201170918090533</v>
       </c>
       <c r="B6" s="0">
-        <v>0.19463226266036848</v>
+        <v>0.13758461085295529</v>
       </c>
       <c r="C6" s="0">
-        <v>1.5829230892441168</v>
+        <v>1.5836854626595922</v>
       </c>
       <c r="D6" s="0">
-        <v>0.016370899689140885</v>
+        <v>0.023753509742121079</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>0.63861944140637905</v>
+      </c>
+      <c r="B7" s="0">
+        <v>0.16064875761773398</v>
+      </c>
+      <c r="C7" s="0">
+        <v>1.5794604693861756</v>
+      </c>
+      <c r="D7" s="0">
+        <v>0.024814225789448932</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>0.80509763204284068</v>
+      </c>
+      <c r="B8" s="0">
+        <v>0.18463605534635863</v>
+      </c>
+      <c r="C8" s="0">
+        <v>1.5841617982713447</v>
+      </c>
+      <c r="D8" s="0">
+        <v>0.0026225649853001075</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>0.32040703415587396</v>
+      </c>
+      <c r="B9" s="0">
+        <v>0.1999961495656345</v>
+      </c>
+      <c r="C9" s="0">
+        <v>1.5800046564561681</v>
+      </c>
+      <c r="D9" s="0">
+        <v>0.044421447363002263</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>0.7824184700928789</v>
+      </c>
+      <c r="B10" s="0">
+        <v>0.17318614191373466</v>
+      </c>
+      <c r="C10" s="0">
+        <v>1.5805896675332478</v>
+      </c>
+      <c r="D10" s="0">
+        <v>0.0071493408222710443</v>
       </c>
     </row>
   </sheetData>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -53,153 +53,97 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="true"/>
-    <col min="2" max="2" width="13.7109375" customWidth="true"/>
+    <col min="2" max="2" width="12.7109375" customWidth="true"/>
     <col min="3" max="3" width="11.7109375" customWidth="true"/>
     <col min="4" max="4" width="15.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0">
-        <v>0.33376862047222772</v>
+        <v>0.61585568404864499</v>
       </c>
       <c r="B1" s="0">
-        <v>0.028419780335263316</v>
+        <v>0.12478348829765686</v>
       </c>
       <c r="C1" s="0">
-        <v>1.5886060698980584</v>
+        <v>1.5402166469505407</v>
       </c>
       <c r="D1" s="0">
-        <v>0.00089436556506111123</v>
+        <v>4.6140866627988299e-17</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>0.3555142389497456</v>
+        <v>0.62009833355690314</v>
       </c>
       <c r="B2" s="0">
-        <v>0.025867121052302759</v>
+        <v>0.11348388530537551</v>
       </c>
       <c r="C2" s="0">
-        <v>1.5998231828576677</v>
+        <v>1.4600004623528557</v>
       </c>
       <c r="D2" s="0">
-        <v>0.0047206779890769154</v>
+        <v>0.00021703295963737887</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.6878218073941077</v>
+        <v>0.68391317473059643</v>
       </c>
       <c r="B3" s="0">
-        <v>0.034125252229147376</v>
+        <v>0.15381951418329837</v>
       </c>
       <c r="C3" s="0">
-        <v>1.5794913011571994</v>
+        <v>1.439265940382809</v>
       </c>
       <c r="D3" s="0">
-        <v>0.00017308635482584788</v>
+        <v>7.9730603476053955e-18</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.82615525908195564</v>
+        <v>0.77607030962302415</v>
       </c>
       <c r="B4" s="0">
-        <v>0.069401042863820414</v>
+        <v>0.18257272688618925</v>
       </c>
       <c r="C4" s="0">
-        <v>1.5919747898389367</v>
+        <v>1.4140274483039532</v>
       </c>
       <c r="D4" s="0">
-        <v>0.0010618026526831288</v>
+        <v>5.2205527619378083e-25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.69615947991023996</v>
+        <v>0.56013196807389265</v>
       </c>
       <c r="B5" s="0">
-        <v>0.10071391548769121</v>
+        <v>0.11354057192350756</v>
       </c>
       <c r="C5" s="0">
-        <v>1.5905381284842586</v>
+        <v>1.4388737273319911</v>
       </c>
       <c r="D5" s="0">
-        <v>0.0039969747079750652</v>
+        <v>8.156006566467007e-05</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.51201170918090533</v>
+        <v>0.75468542368527625</v>
       </c>
       <c r="B6" s="0">
-        <v>0.13758461085295529</v>
+        <v>0.17603000510375619</v>
       </c>
       <c r="C6" s="0">
-        <v>1.5836854626595922</v>
+        <v>1.3710404458956804</v>
       </c>
       <c r="D6" s="0">
-        <v>0.023753509742121079</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0">
-        <v>0.63861944140637905</v>
-      </c>
-      <c r="B7" s="0">
-        <v>0.16064875761773398</v>
-      </c>
-      <c r="C7" s="0">
-        <v>1.5794604693861756</v>
-      </c>
-      <c r="D7" s="0">
-        <v>0.024814225789448932</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0">
-        <v>0.80509763204284068</v>
-      </c>
-      <c r="B8" s="0">
-        <v>0.18463605534635863</v>
-      </c>
-      <c r="C8" s="0">
-        <v>1.5841617982713447</v>
-      </c>
-      <c r="D8" s="0">
-        <v>0.0026225649853001075</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0">
-        <v>0.32040703415587396</v>
-      </c>
-      <c r="B9" s="0">
-        <v>0.1999961495656345</v>
-      </c>
-      <c r="C9" s="0">
-        <v>1.5800046564561681</v>
-      </c>
-      <c r="D9" s="0">
-        <v>0.044421447363002263</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0">
-        <v>0.7824184700928789</v>
-      </c>
-      <c r="B10" s="0">
-        <v>0.17318614191373466</v>
-      </c>
-      <c r="C10" s="0">
-        <v>1.5805896675332478</v>
-      </c>
-      <c r="D10" s="0">
-        <v>0.0071493408222710443</v>
+        <v>4.1298489952310973e-21</v>
       </c>
     </row>
   </sheetData>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -64,86 +64,86 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="0">
-        <v>0.61585568404864499</v>
+        <v>0.68118702694274647</v>
       </c>
       <c r="B1" s="0">
-        <v>0.12478348829765686</v>
+        <v>0.11069439685610816</v>
       </c>
       <c r="C1" s="0">
-        <v>1.5402166469505407</v>
+        <v>1.5797576119086036</v>
       </c>
       <c r="D1" s="0">
-        <v>4.6140866627988299e-17</v>
+        <v>0.00041736092682460039</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>0.62009833355690314</v>
+        <v>0.37093282497834851</v>
       </c>
       <c r="B2" s="0">
-        <v>0.11348388530537551</v>
+        <v>0.17455942719844422</v>
       </c>
       <c r="C2" s="0">
-        <v>1.4600004623528557</v>
+        <v>1.5812390407904158</v>
       </c>
       <c r="D2" s="0">
-        <v>0.00021703295963737887</v>
+        <v>0.00026759736791444582</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.68391317473059643</v>
+        <v>0.61813795433225582</v>
       </c>
       <c r="B3" s="0">
-        <v>0.15381951418329837</v>
+        <v>0.17325196279387556</v>
       </c>
       <c r="C3" s="0">
-        <v>1.439265940382809</v>
+        <v>1.5785590974767594</v>
       </c>
       <c r="D3" s="0">
-        <v>7.9730603476053955e-18</v>
+        <v>0.00073911050691437958</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.77607030962302415</v>
+        <v>0.76314101264820078</v>
       </c>
       <c r="B4" s="0">
-        <v>0.18257272688618925</v>
+        <v>0.1999999999999775</v>
       </c>
       <c r="C4" s="0">
-        <v>1.4140274483039532</v>
+        <v>1.5990499161137131</v>
       </c>
       <c r="D4" s="0">
-        <v>5.2205527619378083e-25</v>
+        <v>0.0024474851507129106</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.56013196807389265</v>
+        <v>0.26631059051539396</v>
       </c>
       <c r="B5" s="0">
-        <v>0.11354057192350756</v>
+        <v>0.19999999999170265</v>
       </c>
       <c r="C5" s="0">
-        <v>1.4388737273319911</v>
+        <v>1.5808428498536367</v>
       </c>
       <c r="D5" s="0">
-        <v>8.156006566467007e-05</v>
+        <v>0.0043007979121243338</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.75468542368527625</v>
+        <v>0.75381931983068728</v>
       </c>
       <c r="B6" s="0">
-        <v>0.17603000510375619</v>
+        <v>0.19999999999979604</v>
       </c>
       <c r="C6" s="0">
-        <v>1.3710404458956804</v>
+        <v>1.589211474581179</v>
       </c>
       <c r="D6" s="0">
-        <v>4.1298489952310973e-21</v>
+        <v>0.015559916060650748</v>
       </c>
     </row>
   </sheetData>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -53,97 +53,200 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="true"/>
-    <col min="2" max="2" width="12.7109375" customWidth="true"/>
+    <col min="2" max="2" width="13.7109375" customWidth="true"/>
     <col min="3" max="3" width="11.7109375" customWidth="true"/>
-    <col min="4" max="4" width="15.7109375" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" customWidth="true"/>
+    <col min="5" max="5" width="13.7109375" customWidth="true"/>
+    <col min="6" max="6" width="11.7109375" customWidth="true"/>
+    <col min="7" max="7" width="15.7109375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0">
-        <v>0.68118702694274647</v>
+        <v>0.99999999999997768</v>
       </c>
       <c r="B1" s="0">
-        <v>0.11069439685610816</v>
+        <v>0.14311583172578318</v>
       </c>
       <c r="C1" s="0">
-        <v>1.5797576119086036</v>
+        <v>2.55346315054845</v>
       </c>
       <c r="D1" s="0">
-        <v>0.00041736092682460039</v>
+        <v>0.46658200825580193</v>
+      </c>
+      <c r="E1" s="0">
+        <v>0.020000000000023898</v>
+      </c>
+      <c r="F1" s="0">
+        <v>4.2172044931036767</v>
+      </c>
+      <c r="G1" s="0">
+        <v>0.011683698134950406</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>0.37093282497834851</v>
+        <v>0.56702430832646111</v>
       </c>
       <c r="B2" s="0">
-        <v>0.17455942719844422</v>
+        <v>0.18135171334663899</v>
       </c>
       <c r="C2" s="0">
-        <v>1.5812390407904158</v>
+        <v>1.1318375242858576</v>
       </c>
       <c r="D2" s="0">
-        <v>0.00026759736791444582</v>
+        <v>0.99999999954503005</v>
+      </c>
+      <c r="E2" s="0">
+        <v>0.12230488043600211</v>
+      </c>
+      <c r="F2" s="0">
+        <v>3.4858686520661877</v>
+      </c>
+      <c r="G2" s="0">
+        <v>0.01036710516471954</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.61813795433225582</v>
+        <v>0.9999999999999778</v>
       </c>
       <c r="B3" s="0">
-        <v>0.17325196279387556</v>
+        <v>0.11135301802516993</v>
       </c>
       <c r="C3" s="0">
-        <v>1.5785590974767594</v>
+        <v>2.4898076531850148</v>
       </c>
       <c r="D3" s="0">
-        <v>0.00073911050691437958</v>
+        <v>0.45533114592371948</v>
+      </c>
+      <c r="E3" s="0">
+        <v>0.020000000000028637</v>
+      </c>
+      <c r="F3" s="0">
+        <v>4.8812818080686222</v>
+      </c>
+      <c r="G3" s="0">
+        <v>0.019737605556386574</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.76314101264820078</v>
+        <v>0.19030564033185321</v>
       </c>
       <c r="B4" s="0">
-        <v>0.1999999999999775</v>
+        <v>0.19987920042442461</v>
       </c>
       <c r="C4" s="0">
-        <v>1.5990499161137131</v>
+        <v>2.4500696700579727</v>
       </c>
       <c r="D4" s="0">
-        <v>0.0024474851507129106</v>
+        <v>0.55450803254305081</v>
+      </c>
+      <c r="E4" s="0">
+        <v>0.090565680530742418</v>
+      </c>
+      <c r="F4" s="0">
+        <v>4.0339352820472207</v>
+      </c>
+      <c r="G4" s="0">
+        <v>0.001619745021370154</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.26631059051539396</v>
+        <v>0.37100883081175262</v>
       </c>
       <c r="B5" s="0">
-        <v>0.19999999999170265</v>
+        <v>0.19999999999995952</v>
       </c>
       <c r="C5" s="0">
-        <v>1.5808428498536367</v>
+        <v>2.5754335153756758</v>
       </c>
       <c r="D5" s="0">
-        <v>0.0043007979121243338</v>
+        <v>0.92618934429340338</v>
+      </c>
+      <c r="E5" s="0">
+        <v>0.085998425103691836</v>
+      </c>
+      <c r="F5" s="0">
+        <v>3.975547258275864</v>
+      </c>
+      <c r="G5" s="0">
+        <v>0.00027827099281207626</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.75381931983068728</v>
+        <v>0.99999730124594732</v>
       </c>
       <c r="B6" s="0">
-        <v>0.19999999999979604</v>
+        <v>0.076288075645727774</v>
       </c>
       <c r="C6" s="0">
-        <v>1.589211474581179</v>
+        <v>3.9043238063600754</v>
       </c>
       <c r="D6" s="0">
-        <v>0.015559916060650748</v>
+        <v>0.44724022848456108</v>
+      </c>
+      <c r="E6" s="0">
+        <v>0.029797040553857346</v>
+      </c>
+      <c r="F6" s="0">
+        <v>1.7268607966678369</v>
+      </c>
+      <c r="G6" s="0">
+        <v>0.0029143270943843805</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0">
+        <v>0.98865521952038438</v>
+      </c>
+      <c r="B7" s="0">
+        <v>0.19994749621208607</v>
+      </c>
+      <c r="C7" s="0">
+        <v>3.5071063879653921</v>
+      </c>
+      <c r="D7" s="0">
+        <v>0.98154329504869542</v>
+      </c>
+      <c r="E7" s="0">
+        <v>0.1670549972682682</v>
+      </c>
+      <c r="F7" s="0">
+        <v>3.6796606766268511</v>
+      </c>
+      <c r="G7" s="0">
+        <v>117.30863766147816</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="0">
+        <v>0.99881193034726823</v>
+      </c>
+      <c r="B8" s="0">
+        <v>0.19999784874519838</v>
+      </c>
+      <c r="C8" s="0">
+        <v>3.5528287332481669</v>
+      </c>
+      <c r="D8" s="0">
+        <v>0.99813104811372055</v>
+      </c>
+      <c r="E8" s="0">
+        <v>0.19999740952861822</v>
+      </c>
+      <c r="F8" s="0">
+        <v>3.5545168555149629</v>
+      </c>
+      <c r="G8" s="0">
+        <v>64.880143661048137</v>
       </c>
     </row>
   </sheetData>

--- a/testdata.xlsx
+++ b/testdata.xlsx
@@ -53,200 +53,361 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="true"/>
-    <col min="2" max="2" width="13.7109375" customWidth="true"/>
-    <col min="3" max="3" width="11.7109375" customWidth="true"/>
-    <col min="4" max="4" width="12.7109375" customWidth="true"/>
-    <col min="5" max="5" width="13.7109375" customWidth="true"/>
-    <col min="6" max="6" width="11.7109375" customWidth="true"/>
-    <col min="7" max="7" width="15.7109375" customWidth="true"/>
+    <col min="1" max="1" width="12.453125" customWidth="true"/>
+    <col min="2" max="2" width="12.453125" customWidth="true"/>
+    <col min="3" max="3" width="12.453125" customWidth="true"/>
+    <col min="4" max="4" width="12.453125" customWidth="true"/>
+    <col min="5" max="5" width="13.453125" customWidth="true"/>
+    <col min="6" max="6" width="11.453125" customWidth="true"/>
+    <col min="7" max="7" width="15.08984375" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0">
-        <v>0.99999999999997768</v>
+        <v>0.80459439661477272</v>
       </c>
       <c r="B1" s="0">
-        <v>0.14311583172578318</v>
+        <v>0.1992381358025806</v>
       </c>
       <c r="C1" s="0">
-        <v>2.55346315054845</v>
+        <v>0.7854008032566997</v>
       </c>
       <c r="D1" s="0">
-        <v>0.46658200825580193</v>
+        <v>0.79565762498643433</v>
       </c>
       <c r="E1" s="0">
-        <v>0.020000000000023898</v>
+        <v>0.099847934727331528</v>
       </c>
       <c r="F1" s="0">
-        <v>4.2172044931036767</v>
+        <v>1.0479744329275666</v>
       </c>
       <c r="G1" s="0">
-        <v>0.011683698134950406</v>
+        <v>3.5104149658778439e-09</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0">
-        <v>0.56702430832646111</v>
+        <v>0.42253083674772718</v>
       </c>
       <c r="B2" s="0">
-        <v>0.18135171334663899</v>
+        <v>0.11530167443591706</v>
       </c>
       <c r="C2" s="0">
-        <v>1.1318375242858576</v>
+        <v>0.70506515162392103</v>
       </c>
       <c r="D2" s="0">
-        <v>0.99999999954503005</v>
+        <v>0.43421226370678284</v>
       </c>
       <c r="E2" s="0">
-        <v>0.12230488043600211</v>
+        <v>0.02729316418142598</v>
       </c>
       <c r="F2" s="0">
-        <v>3.4858686520661877</v>
+        <v>2.4050083617676661</v>
       </c>
       <c r="G2" s="0">
-        <v>0.01036710516471954</v>
+        <v>5.9892618416018369e-09</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0">
-        <v>0.9999999999999778</v>
+        <v>0.69999991151809482</v>
       </c>
       <c r="B3" s="0">
-        <v>0.11135301802516993</v>
+        <v>0.16000000863655572</v>
       </c>
       <c r="C3" s="0">
-        <v>2.4898076531850148</v>
+        <v>0.78500000252435442</v>
       </c>
       <c r="D3" s="0">
-        <v>0.45533114592371948</v>
+        <v>0.29999991089417194</v>
       </c>
       <c r="E3" s="0">
-        <v>0.020000000000028637</v>
+        <v>0.059999997489929228</v>
       </c>
       <c r="F3" s="0">
-        <v>4.8812818080686222</v>
+        <v>3.6649999751165003</v>
       </c>
       <c r="G3" s="0">
-        <v>0.019737605556386574</v>
+        <v>1.0909824643738951e-15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0">
-        <v>0.19030564033185321</v>
+        <v>0.3009611661307921</v>
       </c>
       <c r="B4" s="0">
-        <v>0.19987920042442461</v>
+        <v>0.19896679420951074</v>
       </c>
       <c r="C4" s="0">
-        <v>2.4500696700579727</v>
+        <v>0.7849745072694736</v>
       </c>
       <c r="D4" s="0">
-        <v>0.55450803254305081</v>
+        <v>0.70094909501649061</v>
       </c>
       <c r="E4" s="0">
-        <v>0.090565680530742418</v>
+        <v>0.020000000863018706</v>
       </c>
       <c r="F4" s="0">
-        <v>4.0339352820472207</v>
+        <v>3.6653714190284772</v>
       </c>
       <c r="G4" s="0">
-        <v>0.001619745021370154</v>
+        <v>4.9101564903490365e-09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0">
-        <v>0.37100883081175262</v>
+        <v>0.2815296165003861</v>
       </c>
       <c r="B5" s="0">
-        <v>0.19999999999995952</v>
+        <v>0.16587803798070824</v>
       </c>
       <c r="C5" s="0">
-        <v>2.5754335153756758</v>
+        <v>3.2615933570026234</v>
       </c>
       <c r="D5" s="0">
-        <v>0.92618934429340338</v>
+        <v>0.97087507013845431</v>
       </c>
       <c r="E5" s="0">
-        <v>0.085998425103691836</v>
+        <v>0.06205538372217264</v>
       </c>
       <c r="F5" s="0">
-        <v>3.975547258275864</v>
+        <v>1.1246669081357583</v>
       </c>
       <c r="G5" s="0">
-        <v>0.00027827099281207626</v>
+        <v>2.4768334700847367e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0">
-        <v>0.99999730124594732</v>
+        <v>0.41209855599085893</v>
       </c>
       <c r="B6" s="0">
-        <v>0.076288075645727774</v>
+        <v>0.17585029813770131</v>
       </c>
       <c r="C6" s="0">
-        <v>3.9043238063600754</v>
+        <v>2.683591259674142</v>
       </c>
       <c r="D6" s="0">
-        <v>0.44724022848456108</v>
+        <v>0.32637360623158668</v>
       </c>
       <c r="E6" s="0">
-        <v>0.029797040553857346</v>
+        <v>0.032851432016926946</v>
       </c>
       <c r="F6" s="0">
-        <v>1.7268607966678369</v>
+        <v>1.0118662022021869</v>
       </c>
       <c r="G6" s="0">
-        <v>0.0029143270943843805</v>
+        <v>3.5464490562753011e-12</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0">
-        <v>0.98865521952038438</v>
+        <v>0.80001212959278289</v>
       </c>
       <c r="B7" s="0">
-        <v>0.19994749621208607</v>
+        <v>0.17999758469295529</v>
       </c>
       <c r="C7" s="0">
-        <v>3.5071063879653921</v>
+        <v>2.6180009473505836</v>
       </c>
       <c r="D7" s="0">
-        <v>0.98154329504869542</v>
+        <v>0.69998754364245375</v>
       </c>
       <c r="E7" s="0">
-        <v>0.1670549972682682</v>
+        <v>0.0600003462916349</v>
       </c>
       <c r="F7" s="0">
-        <v>3.6796606766268511</v>
+        <v>2.3559954101805096</v>
       </c>
       <c r="G7" s="0">
-        <v>117.30863766147816</v>
+        <v>2.4943012126454787e-12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0">
-        <v>0.99881193034726823</v>
+        <v>0.70021064978444814</v>
       </c>
       <c r="B8" s="0">
-        <v>0.19999784874519838</v>
+        <v>0.19987824072678015</v>
       </c>
       <c r="C8" s="0">
-        <v>3.5528287332481669</v>
+        <v>2.6180242249506462</v>
       </c>
       <c r="D8" s="0">
-        <v>0.99813104811372055</v>
+        <v>0.79976265071808872</v>
       </c>
       <c r="E8" s="0">
-        <v>0.19999740952861822</v>
+        <v>0.020006221041329139</v>
       </c>
       <c r="F8" s="0">
-        <v>3.5545168555149629</v>
+        <v>2.3559233299927484</v>
       </c>
       <c r="G8" s="0">
-        <v>64.880143661048137</v>
+        <v>1.3565019698561697e-09</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0">
+        <v>0.39771602234777886</v>
+      </c>
+      <c r="B9" s="0">
+        <v>0.14683885702047816</v>
+      </c>
+      <c r="C9" s="0">
+        <v>1.7402995903197682</v>
+      </c>
+      <c r="D9" s="0">
+        <v>0.89411116903465016</v>
+      </c>
+      <c r="E9" s="0">
+        <v>0.08859639605382813</v>
+      </c>
+      <c r="F9" s="0">
+        <v>3.2997171006605486</v>
+      </c>
+      <c r="G9" s="0">
+        <v>1.8666147665328264e-10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0">
+        <v>0.60238529013818154</v>
+      </c>
+      <c r="B10" s="0">
+        <v>0.19940246597952568</v>
+      </c>
+      <c r="C10" s="0">
+        <v>2.6190825556101371</v>
+      </c>
+      <c r="D10" s="0">
+        <v>0.49827911476900433</v>
+      </c>
+      <c r="E10" s="0">
+        <v>0.099841994511341986</v>
+      </c>
+      <c r="F10" s="0">
+        <v>3.6685815077410004</v>
+      </c>
+      <c r="G10" s="0">
+        <v>5.3374819543237143e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0">
+        <v>0.70000027317438063</v>
+      </c>
+      <c r="B11" s="0">
+        <v>0.11999997954241741</v>
+      </c>
+      <c r="C11" s="0">
+        <v>3.9270000527619575</v>
+      </c>
+      <c r="D11" s="0">
+        <v>0.70000027412587429</v>
+      </c>
+      <c r="E11" s="0">
+        <v>0.020000021719603203</v>
+      </c>
+      <c r="F11" s="0">
+        <v>1.0469999507260488</v>
+      </c>
+      <c r="G11" s="0">
+        <v>1.6781897571098314e-18</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0">
+        <v>0.80001060841674076</v>
+      </c>
+      <c r="B12" s="0">
+        <v>0.19999522314881604</v>
+      </c>
+      <c r="C12" s="0">
+        <v>3.9269989193499684</v>
+      </c>
+      <c r="D12" s="0">
+        <v>0.40001214192881018</v>
+      </c>
+      <c r="E12" s="0">
+        <v>0.039999539921724739</v>
+      </c>
+      <c r="F12" s="0">
+        <v>1.0469927314510672</v>
+      </c>
+      <c r="G12" s="0">
+        <v>5.4347264862683872e-12</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0">
+        <v>0.30390698606553773</v>
+      </c>
+      <c r="B13" s="0">
+        <v>0.19790422385616963</v>
+      </c>
+      <c r="C13" s="0">
+        <v>3.9092201032808753</v>
+      </c>
+      <c r="D13" s="0">
+        <v>0.29467310384944195</v>
+      </c>
+      <c r="E13" s="0">
+        <v>0.098139108040604023</v>
+      </c>
+      <c r="F13" s="0">
+        <v>2.3425566440281873</v>
+      </c>
+      <c r="G13" s="0">
+        <v>7.7875052163394106e-09</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0">
+        <v>0.79999948266256493</v>
+      </c>
+      <c r="B14" s="0">
+        <v>0.16000006496401051</v>
+      </c>
+      <c r="C14" s="0">
+        <v>3.9270000564829193</v>
+      </c>
+      <c r="D14" s="0">
+        <v>0.8000005317210741</v>
+      </c>
+      <c r="E14" s="0">
+        <v>0.020000030047118991</v>
+      </c>
+      <c r="F14" s="0">
+        <v>3.6650001540665822</v>
+      </c>
+      <c r="G14" s="0">
+        <v>5.7988210455230476e-15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="0">
+        <v>0.40104277950761691</v>
+      </c>
+      <c r="B15" s="0">
+        <v>0.19919035911958893</v>
+      </c>
+      <c r="C15" s="0">
+        <v>3.9271370717190464</v>
+      </c>
+      <c r="D15" s="0">
+        <v>0.79898434228854676</v>
+      </c>
+      <c r="E15" s="0">
+        <v>0.060044486763447404</v>
+      </c>
+      <c r="F15" s="0">
+        <v>3.6645499793103151</v>
+      </c>
+      <c r="G15" s="0">
+        <v>1.1799087334460409e-08</v>
       </c>
     </row>
   </sheetData>
